--- a/output/pdf_financials_xlsx/LGHT.xlsx
+++ b/output/pdf_financials_xlsx/LGHT.xlsx
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.293617</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.293617</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.293617</v>
       </c>
     </row>
     <row r="93">
@@ -3015,7 +3015,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3378,7 +3382,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.293617</v>
       </c>

--- a/output/pdf_financials_xlsx/LGHT.xlsx
+++ b/output/pdf_financials_xlsx/LGHT.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.603117</v>
+        <v>0.784442</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.158558</v>
+        <v>0.249371</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.174261</v>
+        <v>0.375657</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.603117</v>
+        <v>-0.784442</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.158558</v>
+        <v>-0.249371</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.174261</v>
+        <v>-0.375657</v>
       </c>
     </row>
     <row r="12">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003085</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.212222</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003085</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.212222</v>
       </c>
     </row>
     <row r="37">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.020671</v>
+        <v>0.020654</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.003085</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">

--- a/output/pdf_financials_xlsx/LGHT.xlsx
+++ b/output/pdf_financials_xlsx/LGHT.xlsx
@@ -695,7 +695,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.011447</v>
+        <v>-0.011447</v>
       </c>
     </row>
     <row r="18">
@@ -3607,7 +3607,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4708,7 +4712,11 @@
           <t>Deferred income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
